--- a/artfynd/A 22871-2026 artfynd.xlsx
+++ b/artfynd/A 22871-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134756662</v>
+        <v>135427171</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>93271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100001</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467121</v>
+        <v>467048</v>
       </c>
       <c r="R2" t="n">
-        <v>6550565</v>
+        <v>6550538</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -745,22 +747,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:09</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Förra årets fk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +776,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134760346</v>
+        <v>134756662</v>
       </c>
       <c r="B3" t="n">
         <v>57896</v>
@@ -827,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467105</v>
+        <v>467121</v>
       </c>
       <c r="R3" t="n">
-        <v>6550506</v>
+        <v>6550565</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +865,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>06:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>06:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,27 +907,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134756784</v>
+        <v>134760346</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -939,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467121</v>
+        <v>467105</v>
       </c>
       <c r="R4" t="n">
-        <v>6550565</v>
+        <v>6550506</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,27 +977,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Noterad 163 ggr under perioden.</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,27 +1019,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134760159</v>
+        <v>135431365</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1044,7 +1047,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1056,13 +1068,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467105</v>
+        <v>467110</v>
       </c>
       <c r="R5" t="n">
-        <v>6550506</v>
+        <v>6550492</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,27 +1098,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>04:46</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Noterad 246 ggr under perioden.</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1130,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134760412</v>
+        <v>134756784</v>
       </c>
       <c r="B6" t="n">
         <v>57972</v>
@@ -1173,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467132</v>
+        <v>467121</v>
       </c>
       <c r="R6" t="n">
-        <v>6550557</v>
+        <v>6550565</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1203,27 +1200,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>73 inspelningar under perioden</t>
+          <t>Noterad 163 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,7 +1247,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134761010</v>
+        <v>134760159</v>
       </c>
       <c r="B7" t="n">
         <v>57972</v>
@@ -1290,13 +1287,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467108</v>
+        <v>467105</v>
       </c>
       <c r="R7" t="n">
-        <v>6550501</v>
+        <v>6550506</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,27 +1317,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>04:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>33 noteringar under perioden</t>
+          <t>Noterad 246 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134760887</v>
+        <v>134760412</v>
       </c>
       <c r="B8" t="n">
-        <v>57921</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1378,16 +1375,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100067</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1396,11 +1393,6 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1412,13 +1404,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467108</v>
+        <v>467132</v>
       </c>
       <c r="R8" t="n">
-        <v>6550501</v>
+        <v>6550557</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,12 +1434,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1449,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>73 inspelningar under perioden</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134756998</v>
+        <v>134761010</v>
       </c>
       <c r="B9" t="n">
-        <v>57776</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,29 +1492,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102118</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1529,13 +1521,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467121</v>
+        <v>467108</v>
       </c>
       <c r="R9" t="n">
-        <v>6550565</v>
+        <v>6550501</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1559,27 +1551,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>02:31</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>02:51</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Noterad 94 ggr under perioden.</t>
+          <t>33 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134760069</v>
+        <v>134760887</v>
       </c>
       <c r="B10" t="n">
-        <v>57776</v>
+        <v>57921</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,27 +1609,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102118</v>
+        <v>100067</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1651,10 +1643,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467105</v>
+        <v>467108</v>
       </c>
       <c r="R10" t="n">
-        <v>6550506</v>
+        <v>6550501</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1681,27 +1673,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22:12</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>03:04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Noterad 632 ggr under perioden.</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,27 +1715,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134760296</v>
+        <v>135427217</v>
       </c>
       <c r="B11" t="n">
-        <v>57796</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1757,29 +1744,27 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467105</v>
+        <v>467009</v>
       </c>
       <c r="R11" t="n">
-        <v>6550506</v>
+        <v>6550481</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,27 +1788,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Noterad 26 ggr under perioden.</t>
+          <t>Färska och äldre ringhack på 3 granar i kanten av storskogen. Torkat savflöde och kåda fr hålen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134758923</v>
+        <v>135428788</v>
       </c>
       <c r="B12" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,39 +1846,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467121</v>
+        <v>467024</v>
       </c>
       <c r="R12" t="n">
-        <v>6550565</v>
+        <v>6550482</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1920,27 +1912,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Noterad 5 ggr under perioden.</t>
+          <t>Färska och äldre ringhack på 3 granar i kanten av storskogen. Torkat savflöde och kåda fr hålen.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1967,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134760241</v>
+        <v>135428820</v>
       </c>
       <c r="B13" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,32 +1970,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2012,10 +2003,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467105</v>
+        <v>467019</v>
       </c>
       <c r="R13" t="n">
-        <v>6550506</v>
+        <v>6550474</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2042,27 +2033,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Noterad 50 ggr under perioden.</t>
+          <t>Färska och äldre ringhack på 3 granar i kanten av storskogen. Torkat savflöde och kåda fr hålen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2089,35 +2080,40 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134760431</v>
+        <v>134756998</v>
       </c>
       <c r="B14" t="n">
-        <v>58136</v>
+        <v>57776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -2129,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467132</v>
+        <v>467121</v>
       </c>
       <c r="R14" t="n">
-        <v>6550557</v>
+        <v>6550565</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2159,27 +2155,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>02:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>02:51</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5 noteringar under perioden</t>
+          <t>Noterad 94 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2206,35 +2202,40 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134760517</v>
+        <v>134760069</v>
       </c>
       <c r="B15" t="n">
-        <v>58136</v>
+        <v>57776</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -2246,13 +2247,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467086</v>
+        <v>467105</v>
       </c>
       <c r="R15" t="n">
-        <v>6550652</v>
+        <v>6550506</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2276,27 +2277,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>03:04</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>8 noteringar under perioden</t>
+          <t>Noterad 632 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2323,35 +2324,44 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134761030</v>
+        <v>135431405</v>
       </c>
       <c r="B16" t="n">
-        <v>58136</v>
+        <v>57776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -2363,13 +2373,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467108</v>
+        <v>467110</v>
       </c>
       <c r="R16" t="n">
-        <v>6550501</v>
+        <v>6550492</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2393,27 +2403,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>07:41</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>13 noteringar under perioden</t>
+          <t>Noterad 586 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2440,27 +2440,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134757317</v>
+        <v>134760296</v>
       </c>
       <c r="B17" t="n">
-        <v>58131</v>
+        <v>57796</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103023</v>
+        <v>102976</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2469,6 +2469,11 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -2480,13 +2485,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467121</v>
+        <v>467105</v>
       </c>
       <c r="R17" t="n">
-        <v>6550565</v>
+        <v>6550506</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2515,22 +2520,22 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Noterad 47 ggr under perioden.</t>
+          <t>Noterad 26 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2557,40 +2562,35 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134760264</v>
+        <v>134758923</v>
       </c>
       <c r="B18" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -2602,10 +2602,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467105</v>
+        <v>467121</v>
       </c>
       <c r="R18" t="n">
-        <v>6550506</v>
+        <v>6550565</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2632,27 +2632,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Noterad 82 ggr under perioden.</t>
+          <t>Noterad 5 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2679,35 +2679,40 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134760456</v>
+        <v>134760241</v>
       </c>
       <c r="B19" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -2719,10 +2724,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467132</v>
+        <v>467105</v>
       </c>
       <c r="R19" t="n">
-        <v>6550557</v>
+        <v>6550506</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2749,27 +2754,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>138 noteringar under perioden</t>
+          <t>Noterad 50 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2796,45 +2801,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134759286</v>
+        <v>134760431</v>
       </c>
       <c r="B20" t="n">
-        <v>106324</v>
+        <v>58136</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467075</v>
+        <v>467132</v>
       </c>
       <c r="R20" t="n">
-        <v>6550590</v>
+        <v>6550557</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2861,22 +2871,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>5 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2900,6 +2915,1029 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134760517</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>467086</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6550652</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>8 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134761030</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>467108</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6550501</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>13 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135430105</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>467083</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6550660</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135431344</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>467110</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6550492</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134757317</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>467121</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6550565</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Noterad 47 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134760264</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>467105</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6550506</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Noterad 82 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134760456</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>467132</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6550557</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>138 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135431454</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>467110</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6550492</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Noterad 72 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134759286</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>467075</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6550590</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22871-2026 artfynd.xlsx
+++ b/artfynd/A 22871-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1598,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134760887</v>
+        <v>135442340</v>
       </c>
       <c r="B10" t="n">
-        <v>57921</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,16 +1609,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100067</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1627,11 +1627,6 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467108</v>
+        <v>467102</v>
       </c>
       <c r="R10" t="n">
-        <v>6550501</v>
+        <v>6550498</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1673,22 +1668,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:05</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Noterad 32 ggr under 5 dagar på en 6-dagarsperiod.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,27 +1705,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135427217</v>
+        <v>134760887</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>57921</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100067</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1744,27 +1734,29 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467009</v>
+        <v>467108</v>
       </c>
       <c r="R11" t="n">
-        <v>6550481</v>
+        <v>6550501</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1788,27 +1780,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på 3 granar i kanten av storskogen. Torkat savflöde och kåda fr hålen.</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,7 +1822,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135428788</v>
+        <v>135427217</v>
       </c>
       <c r="B12" t="n">
         <v>57975</v>
@@ -1863,11 +1850,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
@@ -1882,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467024</v>
+        <v>467009</v>
       </c>
       <c r="R12" t="n">
-        <v>6550482</v>
+        <v>6550481</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1917,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1927,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1959,7 +1942,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135428820</v>
+        <v>135428788</v>
       </c>
       <c r="B13" t="n">
         <v>57975</v>
@@ -1992,21 +1975,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467019</v>
+        <v>467024</v>
       </c>
       <c r="R13" t="n">
-        <v>6550474</v>
+        <v>6550482</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2038,7 +2024,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,7 +2034,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2080,43 +2066,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134756998</v>
+        <v>135428820</v>
       </c>
       <c r="B14" t="n">
-        <v>57776</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102118</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2125,10 +2110,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467121</v>
+        <v>467019</v>
       </c>
       <c r="R14" t="n">
-        <v>6550565</v>
+        <v>6550474</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2155,27 +2140,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>02:31</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>02:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Noterad 94 ggr under perioden.</t>
+          <t>Färska och äldre ringhack på 3 granar i kanten av storskogen. Torkat savflöde och kåda fr hålen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2202,7 +2187,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134760069</v>
+        <v>134756998</v>
       </c>
       <c r="B15" t="n">
         <v>57776</v>
@@ -2247,13 +2232,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467105</v>
+        <v>467121</v>
       </c>
       <c r="R15" t="n">
-        <v>6550506</v>
+        <v>6550565</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2277,27 +2262,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>22:12</t>
+          <t>02:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>03:04</t>
+          <t>02:51</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Noterad 632 ggr under perioden.</t>
+          <t>Noterad 94 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2324,7 +2309,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135431405</v>
+        <v>134760069</v>
       </c>
       <c r="B16" t="n">
         <v>57776</v>
@@ -2352,14 +2337,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2373,10 +2354,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467110</v>
+        <v>467105</v>
       </c>
       <c r="R16" t="n">
-        <v>6550492</v>
+        <v>6550506</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2403,17 +2384,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>22:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>03:04</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Noterad 586 ggr under perioden.</t>
+          <t>Noterad 632 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2440,38 +2431,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134760296</v>
+        <v>135431405</v>
       </c>
       <c r="B17" t="n">
-        <v>57796</v>
+        <v>57776</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102976</v>
+        <v>102118</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2485,10 +2480,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467105</v>
+        <v>467110</v>
       </c>
       <c r="R17" t="n">
-        <v>6550506</v>
+        <v>6550492</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2515,27 +2510,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:09</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Noterad 26 ggr under perioden.</t>
+          <t>Noterad 586 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,35 +2547,40 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134758923</v>
+        <v>135442268</v>
       </c>
       <c r="B18" t="n">
-        <v>58136</v>
+        <v>57776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -2602,13 +2592,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467121</v>
+        <v>467102</v>
       </c>
       <c r="R18" t="n">
-        <v>6550565</v>
+        <v>6550498</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2632,27 +2622,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>06:41</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:16</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Noterad 5 ggr under perioden.</t>
+          <t>Noterad 28 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2679,38 +2659,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134760241</v>
+        <v>134760296</v>
       </c>
       <c r="B19" t="n">
-        <v>58136</v>
+        <v>57796</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>102976</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2730,7 +2710,7 @@
         <v>6550506</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2754,12 +2734,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2769,12 +2749,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Noterad 50 ggr under perioden.</t>
+          <t>Noterad 26 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2801,7 +2781,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134760431</v>
+        <v>134758923</v>
       </c>
       <c r="B20" t="n">
         <v>58136</v>
@@ -2841,10 +2821,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467132</v>
+        <v>467121</v>
       </c>
       <c r="R20" t="n">
-        <v>6550557</v>
+        <v>6550565</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2871,27 +2851,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>5 noteringar under perioden</t>
+          <t>Noterad 5 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2918,7 +2898,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134760517</v>
+        <v>134760241</v>
       </c>
       <c r="B21" t="n">
         <v>58136</v>
@@ -2947,6 +2927,11 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -2958,10 +2943,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467086</v>
+        <v>467105</v>
       </c>
       <c r="R21" t="n">
-        <v>6550652</v>
+        <v>6550506</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2988,27 +2973,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>8 noteringar under perioden</t>
+          <t>Noterad 50 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3035,7 +3020,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134761030</v>
+        <v>134760431</v>
       </c>
       <c r="B22" t="n">
         <v>58136</v>
@@ -3075,10 +3060,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467108</v>
+        <v>467132</v>
       </c>
       <c r="R22" t="n">
-        <v>6550501</v>
+        <v>6550557</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3110,22 +3095,22 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>13 noteringar under perioden</t>
+          <t>5 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3152,7 +3137,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135430105</v>
+        <v>134760517</v>
       </c>
       <c r="B23" t="n">
         <v>58136</v>
@@ -3181,11 +3166,6 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -3197,10 +3177,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467083</v>
+        <v>467086</v>
       </c>
       <c r="R23" t="n">
-        <v>6550660</v>
+        <v>6550652</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3227,12 +3207,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>8 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3259,7 +3254,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135431344</v>
+        <v>134761030</v>
       </c>
       <c r="B24" t="n">
         <v>58136</v>
@@ -3288,11 +3283,6 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -3304,10 +3294,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467110</v>
+        <v>467108</v>
       </c>
       <c r="R24" t="n">
-        <v>6550492</v>
+        <v>6550501</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3334,12 +3324,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>13 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3366,35 +3371,40 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134757317</v>
+        <v>135430105</v>
       </c>
       <c r="B25" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -3406,10 +3416,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467121</v>
+        <v>467083</v>
       </c>
       <c r="R25" t="n">
-        <v>6550565</v>
+        <v>6550660</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3436,27 +3446,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Noterad 47 ggr under perioden.</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3483,38 +3478,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134760264</v>
+        <v>135431344</v>
       </c>
       <c r="B26" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3528,10 +3523,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467105</v>
+        <v>467110</v>
       </c>
       <c r="R26" t="n">
-        <v>6550506</v>
+        <v>6550492</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3558,27 +3553,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>18:44</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Noterad 82 ggr under perioden.</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3605,35 +3585,40 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134760456</v>
+        <v>135442095</v>
       </c>
       <c r="B27" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -3645,10 +3630,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467132</v>
+        <v>467102</v>
       </c>
       <c r="R27" t="n">
-        <v>6550557</v>
+        <v>6550498</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3675,27 +3660,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>06:10</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:39</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>138 noteringar under perioden</t>
+          <t>Noterad 43 ggr under 4 dagar under perioden.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3722,7 +3697,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135431454</v>
+        <v>134757317</v>
       </c>
       <c r="B28" t="n">
         <v>58131</v>
@@ -3751,11 +3726,6 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -3767,10 +3737,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467110</v>
+        <v>467121</v>
       </c>
       <c r="R28" t="n">
-        <v>6550492</v>
+        <v>6550565</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3797,17 +3767,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Noterad 72 ggr under perioden.</t>
+          <t>Noterad 47 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3834,10 +3814,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134759286</v>
+        <v>134760264</v>
       </c>
       <c r="B29" t="n">
-        <v>106324</v>
+        <v>58131</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3845,34 +3825,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>103023</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467075</v>
+        <v>467105</v>
       </c>
       <c r="R29" t="n">
-        <v>6550590</v>
+        <v>6550506</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3899,22 +3889,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Noterad 82 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3938,6 +3933,454 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134760456</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>467132</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6550557</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>138 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135431454</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>467110</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6550492</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Noterad 72 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135442068</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>467102</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6550498</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Noterad 212 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134759286</v>
+      </c>
+      <c r="B33" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>467075</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6550590</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22871-2026 artfynd.xlsx
+++ b/artfynd/A 22871-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4277,10 +4277,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134759286</v>
+        <v>135484901</v>
       </c>
       <c r="B33" t="n">
-        <v>106324</v>
+        <v>56854</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,34 +4288,44 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>205995</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467075</v>
+        <v>467134</v>
       </c>
       <c r="R33" t="n">
-        <v>6550590</v>
+        <v>6550499</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4342,22 +4352,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4381,6 +4391,343 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135485124</v>
+      </c>
+      <c r="B34" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>467134</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6550499</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>23:52</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>23:52</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135484812</v>
+      </c>
+      <c r="B35" t="n">
+        <v>56856</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>467134</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6550499</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134759286</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>467075</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6550590</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22871-2026 artfynd.xlsx
+++ b/artfynd/A 22871-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427171</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134756662</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760346</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1127,6 +1147,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431365</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,6 +1269,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134756784</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1361,6 +1391,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760159</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1478,6 +1513,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760412</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1595,6 +1635,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134761010</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1702,6 +1747,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442340</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1819,6 +1869,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760887</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1939,6 +1994,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427217</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2063,6 +2123,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428788</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2184,6 +2249,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428820</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2306,6 +2376,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134756998</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2428,6 +2503,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760069</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2544,6 +2624,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431405</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2656,6 +2741,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442268</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2778,6 +2868,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760296</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2895,6 +2990,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758923</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3017,6 +3117,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760241</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3134,6 +3239,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760431</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3251,6 +3361,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760517</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3368,6 +3483,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134761030</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3475,6 +3595,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430105</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3582,6 +3707,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431344</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3694,6 +3824,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442095</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3811,6 +3946,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134757317</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3933,6 +4073,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760264</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4050,6 +4195,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760456</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4162,6 +4312,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431454</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4274,6 +4429,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442068</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4391,6 +4551,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484901</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4504,6 +4669,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135485124</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4621,6 +4791,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484812</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4728,8 +4903,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759286</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 22871-2026 artfynd.xlsx
+++ b/artfynd/A 22871-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135427171</v>
       </c>
       <c r="B2" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>135431365</v>
       </c>
       <c r="B5" t="n">
-        <v>57896</v>
+        <v>57901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>135442340</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>135427217</v>
       </c>
       <c r="B12" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>135428788</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>135428820</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>135431405</v>
       </c>
       <c r="B17" t="n">
-        <v>57776</v>
+        <v>57781</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135442268</v>
       </c>
       <c r="B18" t="n">
-        <v>57776</v>
+        <v>57781</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>135430105</v>
       </c>
       <c r="B25" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>135431344</v>
       </c>
       <c r="B26" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>135442095</v>
       </c>
       <c r="B27" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>135431454</v>
       </c>
       <c r="B31" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>135442068</v>
       </c>
       <c r="B32" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135484901</v>
       </c>
       <c r="B33" t="n">
-        <v>56854</v>
+        <v>56859</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>135485124</v>
       </c>
       <c r="B34" t="n">
-        <v>56833</v>
+        <v>56838</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>135484812</v>
       </c>
       <c r="B35" t="n">
-        <v>56856</v>
+        <v>56861</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 22871-2026 artfynd.xlsx
+++ b/artfynd/A 22871-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135427171</v>
       </c>
       <c r="B2" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22871-2026 artfynd.xlsx
+++ b/artfynd/A 22871-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134756662</v>
+        <v>135427171</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>93345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100001</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467121</v>
+        <v>467048</v>
       </c>
       <c r="R2" t="n">
-        <v>6550565</v>
+        <v>6550538</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,22 +752,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:09</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Förra årets fk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,6 +781,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,13 +799,13 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134756662</t>
+          <t>https://artportalen.se/Sighting/135427171</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134760346</v>
+        <v>134756662</v>
       </c>
       <c r="B3" t="n">
         <v>57896</v>
@@ -837,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467105</v>
+        <v>467121</v>
       </c>
       <c r="R3" t="n">
-        <v>6550506</v>
+        <v>6550565</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +875,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>06:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>06:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,33 +916,33 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760346</t>
+          <t>https://artportalen.se/Sighting/134756662</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134756784</v>
+        <v>134760346</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -954,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467121</v>
+        <v>467105</v>
       </c>
       <c r="R4" t="n">
-        <v>6550565</v>
+        <v>6550506</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,27 +992,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Noterad 163 ggr under perioden.</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,33 +1033,33 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134756784</t>
+          <t>https://artportalen.se/Sighting/134760346</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134760159</v>
+        <v>135431365</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>57901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1064,7 +1067,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1076,13 +1088,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467105</v>
+        <v>467110</v>
       </c>
       <c r="R5" t="n">
-        <v>6550506</v>
+        <v>6550492</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,27 +1118,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>04:46</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Noterad 246 ggr under perioden.</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,13 +1149,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760159</t>
+          <t>https://artportalen.se/Sighting/135431365</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134760412</v>
+        <v>134756784</v>
       </c>
       <c r="B6" t="n">
         <v>57972</v>
@@ -1198,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467132</v>
+        <v>467121</v>
       </c>
       <c r="R6" t="n">
-        <v>6550557</v>
+        <v>6550565</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1228,27 +1225,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>73 inspelningar under perioden</t>
+          <t>Noterad 163 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,13 +1271,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760412</t>
+          <t>https://artportalen.se/Sighting/134756784</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134761010</v>
+        <v>134760159</v>
       </c>
       <c r="B7" t="n">
         <v>57972</v>
@@ -1320,13 +1317,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467108</v>
+        <v>467105</v>
       </c>
       <c r="R7" t="n">
-        <v>6550501</v>
+        <v>6550506</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1350,27 +1347,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>04:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>33 noteringar under perioden</t>
+          <t>Noterad 246 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,16 +1393,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134761010</t>
+          <t>https://artportalen.se/Sighting/134760159</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134760887</v>
+        <v>134760412</v>
       </c>
       <c r="B8" t="n">
-        <v>57921</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,16 +1410,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100067</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1431,11 +1428,6 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1447,13 +1439,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467108</v>
+        <v>467132</v>
       </c>
       <c r="R8" t="n">
-        <v>6550501</v>
+        <v>6550557</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1477,12 +1469,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1492,7 +1484,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>73 inspelningar under perioden</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,16 +1515,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760887</t>
+          <t>https://artportalen.se/Sighting/134760412</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134756998</v>
+        <v>134761010</v>
       </c>
       <c r="B9" t="n">
-        <v>57776</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,29 +1532,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102118</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1569,13 +1561,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467121</v>
+        <v>467108</v>
       </c>
       <c r="R9" t="n">
-        <v>6550565</v>
+        <v>6550501</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1599,27 +1591,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>02:31</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>02:51</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Noterad 94 ggr under perioden.</t>
+          <t>33 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1645,16 +1637,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134756998</t>
+          <t>https://artportalen.se/Sighting/134761010</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134760069</v>
+        <v>135442340</v>
       </c>
       <c r="B10" t="n">
-        <v>57776</v>
+        <v>57977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,29 +1654,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102118</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1696,10 +1683,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467105</v>
+        <v>467102</v>
       </c>
       <c r="R10" t="n">
-        <v>6550506</v>
+        <v>6550498</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1726,27 +1713,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>22:12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>03:04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Noterad 632 ggr under perioden.</t>
+          <t>Noterad 32 ggr under 5 dagar på en 6-dagarsperiod.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,33 +1749,33 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760069</t>
+          <t>https://artportalen.se/Sighting/135442340</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134760296</v>
+        <v>134760887</v>
       </c>
       <c r="B11" t="n">
-        <v>57796</v>
+        <v>57921</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102976</v>
+        <v>100067</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1823,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467105</v>
+        <v>467108</v>
       </c>
       <c r="R11" t="n">
-        <v>6550506</v>
+        <v>6550501</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1853,27 +1830,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Noterad 26 ggr under perioden.</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1899,16 +1871,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760296</t>
+          <t>https://artportalen.se/Sighting/134760887</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134758923</v>
+        <v>135427217</v>
       </c>
       <c r="B12" t="n">
-        <v>58136</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,39 +1888,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467121</v>
+        <v>467009</v>
       </c>
       <c r="R12" t="n">
-        <v>6550565</v>
+        <v>6550481</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1975,27 +1950,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Noterad 5 ggr under perioden.</t>
+          <t>Färska och äldre ringhack på 3 granar i kanten av storskogen. Torkat savflöde och kåda fr hålen.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2021,16 +1996,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134758923</t>
+          <t>https://artportalen.se/Sighting/135427217</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134760241</v>
+        <v>135428788</v>
       </c>
       <c r="B13" t="n">
-        <v>58136</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,44 +2013,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467105</v>
+        <v>467024</v>
       </c>
       <c r="R13" t="n">
-        <v>6550506</v>
+        <v>6550482</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2102,27 +2079,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Noterad 50 ggr under perioden.</t>
+          <t>Färska och äldre ringhack på 3 granar i kanten av storskogen. Torkat savflöde och kåda fr hålen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2148,16 +2125,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760241</t>
+          <t>https://artportalen.se/Sighting/135428788</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134760431</v>
+        <v>135428820</v>
       </c>
       <c r="B14" t="n">
-        <v>58136</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2165,27 +2142,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2194,10 +2175,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467132</v>
+        <v>467019</v>
       </c>
       <c r="R14" t="n">
-        <v>6550557</v>
+        <v>6550474</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2224,27 +2205,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5 noteringar under perioden</t>
+          <t>Färska och äldre ringhack på 3 granar i kanten av storskogen. Torkat savflöde och kåda fr hålen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2270,41 +2251,46 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760431</t>
+          <t>https://artportalen.se/Sighting/135428820</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134760517</v>
+        <v>134756998</v>
       </c>
       <c r="B15" t="n">
-        <v>58136</v>
+        <v>57776</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -2316,10 +2302,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467086</v>
+        <v>467121</v>
       </c>
       <c r="R15" t="n">
-        <v>6550652</v>
+        <v>6550565</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2346,27 +2332,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>02:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>02:51</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>8 noteringar under perioden</t>
+          <t>Noterad 94 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2392,41 +2378,46 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760517</t>
+          <t>https://artportalen.se/Sighting/134756998</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134761030</v>
+        <v>134760069</v>
       </c>
       <c r="B16" t="n">
-        <v>58136</v>
+        <v>57776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -2438,13 +2429,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467108</v>
+        <v>467105</v>
       </c>
       <c r="R16" t="n">
-        <v>6550501</v>
+        <v>6550506</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2468,27 +2459,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>03:04</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>13 noteringar under perioden</t>
+          <t>Noterad 632 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2514,16 +2505,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134761030</t>
+          <t>https://artportalen.se/Sighting/134760069</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134757317</v>
+        <v>135431405</v>
       </c>
       <c r="B17" t="n">
-        <v>58131</v>
+        <v>57781</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,24 +2522,33 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103023</v>
+        <v>102118</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467121</v>
+        <v>467110</v>
       </c>
       <c r="R17" t="n">
-        <v>6550565</v>
+        <v>6550492</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2590,27 +2590,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Noterad 47 ggr under perioden.</t>
+          <t>Noterad 586 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2636,16 +2626,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134757317</t>
+          <t>https://artportalen.se/Sighting/135431405</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134760264</v>
+        <v>135442268</v>
       </c>
       <c r="B18" t="n">
-        <v>58131</v>
+        <v>57781</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2653,27 +2643,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103023</v>
+        <v>102118</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2687,13 +2677,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467105</v>
+        <v>467102</v>
       </c>
       <c r="R18" t="n">
-        <v>6550506</v>
+        <v>6550498</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2717,27 +2707,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>18:44</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Noterad 82 ggr under perioden.</t>
+          <t>Noterad 28 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2763,33 +2743,33 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760264</t>
+          <t>https://artportalen.se/Sighting/135442268</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134760456</v>
+        <v>134760296</v>
       </c>
       <c r="B19" t="n">
-        <v>58131</v>
+        <v>57796</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103023</v>
+        <v>102976</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2798,6 +2778,11 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -2809,13 +2794,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467132</v>
+        <v>467105</v>
       </c>
       <c r="R19" t="n">
-        <v>6550557</v>
+        <v>6550506</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2839,27 +2824,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>138 noteringar under perioden</t>
+          <t>Noterad 26 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2885,51 +2870,56 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760456</t>
+          <t>https://artportalen.se/Sighting/134760296</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134759286</v>
+        <v>134758923</v>
       </c>
       <c r="B20" t="n">
-        <v>106324</v>
+        <v>58136</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467075</v>
+        <v>467121</v>
       </c>
       <c r="R20" t="n">
-        <v>6550590</v>
+        <v>6550565</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2956,22 +2946,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Noterad 5 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2996,6 +2991,1919 @@
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758923</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134760241</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>467105</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6550506</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Noterad 50 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760241</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134760431</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>467132</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6550557</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>5 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760431</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134760517</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>467086</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6550652</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>8 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760517</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134761030</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>467108</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6550501</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>13 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134761030</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135430105</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>467083</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6550660</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135430105</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135431344</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>467110</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6550492</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431344</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135442095</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>467102</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6550498</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Noterad 43 ggr under 4 dagar under perioden.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442095</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134757317</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>467121</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6550565</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Noterad 47 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134757317</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134760264</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>467105</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6550506</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Noterad 82 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760264</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134760456</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>467132</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6550557</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>138 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760456</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135431454</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>467110</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6550492</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Noterad 72 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431454</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135442068</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>467102</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6550498</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Noterad 212 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442068</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135484901</v>
+      </c>
+      <c r="B33" t="n">
+        <v>56859</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>467134</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6550499</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484901</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135485124</v>
+      </c>
+      <c r="B34" t="n">
+        <v>56838</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>467134</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6550499</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>23:52</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>23:52</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135485124</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135484812</v>
+      </c>
+      <c r="B35" t="n">
+        <v>56861</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>467134</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6550499</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484812</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134759286</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>467075</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6550590</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134759286</t>
         </is>
@@ -3022,6 +4930,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22871-2026 artfynd.xlsx
+++ b/artfynd/A 22871-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135427171</v>
       </c>
       <c r="B2" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
